--- a/datos/Pendiente Facturar Comparar.xlsx
+++ b/datos/Pendiente Facturar Comparar.xlsx
@@ -2,23 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gonpro/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71D6D20-38A9-A54C-851D-0A824DFC3465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6426A0E3-0122-F24E-A8F3-9728720A2D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34420" yWindow="3060" windowWidth="22940" windowHeight="14820" xr2:uid="{99A9BFE7-FD37-0744-96E5-9F0BD06A67C7}"/>
+    <workbookView xWindow="4420" yWindow="1660" windowWidth="22360" windowHeight="16960" activeTab="1" xr2:uid="{99A9BFE7-FD37-0744-96E5-9F0BD06A67C7}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Analisis" sheetId="1" r:id="rId1"/>
+    <sheet name="GD 1972-1960-1959" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$20:$C$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GD 1972-1960-1959'!$R$1:$S$52</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Analisis!$A$20:$C$42</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <pivotCaches>
+    <pivotCache cacheId="9" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="176">
   <si>
     <t>1994</t>
   </si>
@@ -225,12 +230,421 @@
   <si>
     <t>¿Quieres que ajustemos algo en la app para manejar los casos HES, o es información para carga manual? 👍</t>
   </si>
+  <si>
+    <t>ITEM</t>
+  </si>
+  <si>
+    <t>VALOR UNITARIO ($) ​</t>
+  </si>
+  <si>
+    <t>CANTIDAD</t>
+  </si>
+  <si>
+    <t>SUBTOTAL ($) ​</t>
+  </si>
+  <si>
+    <t>Golilla Plana 1/2 NR ​</t>
+  </si>
+  <si>
+    <t>Golilla Presión 1/2 NR ​</t>
+  </si>
+  <si>
+    <t>Perno Hexagonal Grado 2 1/2 x 1.1/2 NR ​</t>
+  </si>
+  <si>
+    <t>Tuerca Hexagonal Grado 2 1/2 NR ​</t>
+  </si>
+  <si>
+    <t>Perno Hexagonal Grado 2 1/2X1 Pulg ​</t>
+  </si>
+  <si>
+    <t>GD</t>
+  </si>
+  <si>
+    <t>Tuerca Hexagonal Grado 2 3/8 NR</t>
+  </si>
+  <si>
+    <t>Tuerca Hexagonal Grado 2 5/8 NR</t>
+  </si>
+  <si>
+    <t>Golilla Plana 1/4 NR</t>
+  </si>
+  <si>
+    <t>Golilla Plana 3/8 NR</t>
+  </si>
+  <si>
+    <t>Golilla Plana 5/8 NR</t>
+  </si>
+  <si>
+    <t>Golilla Presión 1/4 NR</t>
+  </si>
+  <si>
+    <t>Golilla Presión 3/4 NR</t>
+  </si>
+  <si>
+    <t>Golilla Presión 3/8 NR</t>
+  </si>
+  <si>
+    <t>Golilla Presión 5/8 NR</t>
+  </si>
+  <si>
+    <t>Golilla Plana 3/4 NR</t>
+  </si>
+  <si>
+    <t>Tuerca Hexagonal Grado 2 1/2 NR</t>
+  </si>
+  <si>
+    <t>Golilla Plana 1/2 NR</t>
+  </si>
+  <si>
+    <t>Golilla Presión 1/2 NR</t>
+  </si>
+  <si>
+    <t>Perno Hexagonal Grado 2 1/2 x 1.1/2 NR</t>
+  </si>
+  <si>
+    <t>Perno Hexagonal Grado 2 1/2 x 2 NR</t>
+  </si>
+  <si>
+    <t>Perno Hexagonal Grado 2 1/4 x 1 NR</t>
+  </si>
+  <si>
+    <t>Perno Hexagonal A325 3/4 x 2.1/2 NR</t>
+  </si>
+  <si>
+    <t>Perno Hexagonal Grado 2 3/8 x 1.1/2 NR</t>
+  </si>
+  <si>
+    <t>Perno Hexagonal Grado 2 3/8 x 1 NR</t>
+  </si>
+  <si>
+    <t>Perno Hexagonal Grado 2 3/8 X 3/4" NR</t>
+  </si>
+  <si>
+    <t>Perno Hexagonal Grado 2 5/8 x 4 NR</t>
+  </si>
+  <si>
+    <t>Tuerca Hexagonal Grado 2 1/4 NR</t>
+  </si>
+  <si>
+    <t>Tuerca Hexagonal Grado 2 3/4 NR</t>
+  </si>
+  <si>
+    <t>DESCRIPCION</t>
+  </si>
+  <si>
+    <t>UNIDAD</t>
+  </si>
+  <si>
+    <t>PRECIO UNITARIO</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>TUERCA HEX G-2 1/2"</t>
+  </si>
+  <si>
+    <t>UN</t>
+  </si>
+  <si>
+    <t>GOLILLA PLANA CAL 1/2" ZIN</t>
+  </si>
+  <si>
+    <t>GOLILLA PRESION 1/2 PULG</t>
+  </si>
+  <si>
+    <t>PERNO HEX G2 UNC 1/2-1 1/2</t>
+  </si>
+  <si>
+    <t>GOLILLA PRESION 1/2"</t>
+  </si>
+  <si>
+    <t>PERNO HEX G2 UNC 1/2 X2 1 1/2</t>
+  </si>
+  <si>
+    <t>PERNO HEX 1/4 X1</t>
+  </si>
+  <si>
+    <t>PERNO HEX. A325 3/4" X 2.1/2"</t>
+  </si>
+  <si>
+    <t>PERNO HEX G2 UNC/BSW 3/8-16 1/2</t>
+  </si>
+  <si>
+    <t>PERNO HEX G2 3/8 X1</t>
+  </si>
+  <si>
+    <t>PERNO HEX A 449 T1 UNC TM 3/8 X3/4</t>
+  </si>
+  <si>
+    <t>PERNO HEX G 2 UN 3/8 X1.1/2</t>
+  </si>
+  <si>
+    <t>PERNO HEX G2 5/8X4</t>
+  </si>
+  <si>
+    <t>TUERCA HEX 1/2" CORRIENTE</t>
+  </si>
+  <si>
+    <t>TUERCA HEX 1/4</t>
+  </si>
+  <si>
+    <t>TUERCA HEXAGONAL CORRIENTE UNC 3/4</t>
+  </si>
+  <si>
+    <t>TUERCA HEG CORRIENTE 3/8"</t>
+  </si>
+  <si>
+    <t>TUERCA HEX CORRIENTE 3/8"</t>
+  </si>
+  <si>
+    <t>TUERCA HEX 5/8 CORRIENTE</t>
+  </si>
+  <si>
+    <t>TUERCA HEX CORRIENTE 5/8</t>
+  </si>
+  <si>
+    <t>GOLILLA PLANA CORR ZN 1/4"</t>
+  </si>
+  <si>
+    <t>GOLILLA PLANA CALIB ZN 3/8"</t>
+  </si>
+  <si>
+    <t>GOLILLA PLANA CALIB 5/8"</t>
+  </si>
+  <si>
+    <t>GOLILLA PRESION ZN 1/4"</t>
+  </si>
+  <si>
+    <t>GOLILLA PRESION 3/4"</t>
+  </si>
+  <si>
+    <t>GOLILLA PRESION 3/8"</t>
+  </si>
+  <si>
+    <t>GOLILLA PRESION 5/8"</t>
+  </si>
+  <si>
+    <t>GOLILLA PLANA CAL 1/2" NR</t>
+  </si>
+  <si>
+    <t>GOLILLA PLANA CALIB 3/4"</t>
+  </si>
+  <si>
+    <t>GOLILLA PLANA CAL 3/8" ZIN</t>
+  </si>
+  <si>
+    <t>PERNO HEX G-2 UNC 1/2 X 1</t>
+  </si>
+  <si>
+    <t>PERNO HEX G2 UNC 1/2"X 1 1/2</t>
+  </si>
+  <si>
+    <t>GOLILLA PLANA CALIB ZN 1/2"</t>
+  </si>
+  <si>
+    <t>TUERCA HEX H2 1/2</t>
+  </si>
+  <si>
+    <t>PERNO HEX G-2 UNC ZN 1/2X11/2</t>
+  </si>
+  <si>
+    <t>TUERCA HEX G-2 UNC ZN 1/2"</t>
+  </si>
+  <si>
+    <t>PERNO HEX G-2 UNC 1/2 x 11/2 ZINCADO</t>
+  </si>
+  <si>
+    <t>Etiquetas de fila</t>
+  </si>
+  <si>
+    <t>Total general</t>
+  </si>
+  <si>
+    <t>Promedio de PRECIO UNITARIO</t>
+  </si>
+  <si>
+    <t>DescGD</t>
+  </si>
+  <si>
+    <t>Suma de TOTAL</t>
+  </si>
+  <si>
+    <t>TUERCA HEX G-2 1/2" (SYC-487)</t>
+  </si>
+  <si>
+    <t>616 pend.</t>
+  </si>
+  <si>
+    <t>GOLILLA PLANA CAL 1/2" ZIN (SYC-5528)</t>
+  </si>
+  <si>
+    <t>GOLILLA PRESION 1/2 PULG (SYC-5552)</t>
+  </si>
+  <si>
+    <t>PERNO HEX G2 UNC 1/2-1 1/2 (SYC-8181)</t>
+  </si>
+  <si>
+    <t>120 pend.</t>
+  </si>
+  <si>
+    <t>GOLILLA PRESION 1/2" (SYC-283)</t>
+  </si>
+  <si>
+    <t>PERNO HEX G2 UNC 1/2 X2 1 1/2 (SYC-8202)</t>
+  </si>
+  <si>
+    <t>20 pend.</t>
+  </si>
+  <si>
+    <t>PERNO HEX 1/4 X1 (SYC-8289)</t>
+  </si>
+  <si>
+    <t>40 pend.</t>
+  </si>
+  <si>
+    <t>PERNO HEX. A325 3/4" X 2.1/2" (SYC-14281)</t>
+  </si>
+  <si>
+    <t>80 pend.</t>
+  </si>
+  <si>
+    <t>PERNO HEX G2 UNC/BSW 3/8-16 1/2 (SYC-8246)</t>
+  </si>
+  <si>
+    <t>140 pend.</t>
+  </si>
+  <si>
+    <t>PERNO HEX G2 3/8 X1 (SYC-8246)</t>
+  </si>
+  <si>
+    <t>208 pend.</t>
+  </si>
+  <si>
+    <t>PERNO HEX A449 T1 UNC TM 3/8 X3/4 (SYC-8246)</t>
+  </si>
+  <si>
+    <t>60 pend.</t>
+  </si>
+  <si>
+    <t>PERNO HEX G2 UN 3/8 X1.1/2 (SYC-8246)</t>
+  </si>
+  <si>
+    <t>PERNO HEX G2 5/8X4 (SYC-8314)</t>
+  </si>
+  <si>
+    <t>56 pend.</t>
+  </si>
+  <si>
+    <t>TUERCA HEX 1/2" CORRIENTE (SYC-12166)</t>
+  </si>
+  <si>
+    <t>1.520 pend.</t>
+  </si>
+  <si>
+    <t>TUERCA HEX 1/4 (SYC-12176)</t>
+  </si>
+  <si>
+    <t>TUERCA HEXAGONAL CORRIENTE UNC 3/4 (SYC-12169)</t>
+  </si>
+  <si>
+    <t>TUERCA HEX CORRIENTE 3/8" (SYC-491)</t>
+  </si>
+  <si>
+    <t>180 pend.</t>
+  </si>
+  <si>
+    <t>348 pend.</t>
+  </si>
+  <si>
+    <t>TUERCA HEX 5/8 CORRIENTE (SYC-12175)</t>
+  </si>
+  <si>
+    <t>TUERCA HEX CORRIENTE 5/8 (SYC-12178)</t>
+  </si>
+  <si>
+    <t>156 pend.</t>
+  </si>
+  <si>
+    <t>GOLILLA PLANA CORR ZN 1/4" (SYC-271)</t>
+  </si>
+  <si>
+    <t>GOLILLA PLANA CALIB ZN 3/8" (SYC-266)</t>
+  </si>
+  <si>
+    <t>GOLILLA PLANA CALIB 5/8" (SYC-263)</t>
+  </si>
+  <si>
+    <t>1.400 pend.</t>
+  </si>
+  <si>
+    <t>GOLILLA PRESION ZN 1/4" (SYC-288)</t>
+  </si>
+  <si>
+    <t>GOLILLA PRESION 3/4" (SYC-284)</t>
+  </si>
+  <si>
+    <t>GOLILLA PRESION 3/8" (SYC-285)</t>
+  </si>
+  <si>
+    <t>320 pend.</t>
+  </si>
+  <si>
+    <t>GOLILLA PRESION 5/8" (SYC-286)</t>
+  </si>
+  <si>
+    <t>GOLILLA PLANA CAL 1/2" NR (SYC-5528)</t>
+  </si>
+  <si>
+    <t>GOLILLA PLANA CALIB 3/4" (SYC-261)</t>
+  </si>
+  <si>
+    <t>GOLILLA PLANA CAL 3/8" ZIN (SYC-5530)</t>
+  </si>
+  <si>
+    <t>PERNO HEX G-2 UNC 1/2 X 1 (SYC-8167)</t>
+  </si>
+  <si>
+    <t>268 pend.</t>
+  </si>
+  <si>
+    <t>PERNO HEX G2 UNC 1/2" X 1 1/2 (SYC-8202)</t>
+  </si>
+  <si>
+    <t>4 pend.</t>
+  </si>
+  <si>
+    <t>GOLILLA PLANA CALIB ZN 1/2" (SYC-264)</t>
+  </si>
+  <si>
+    <t>GOLILLA PRESION 1/2" (SYC-287)</t>
+  </si>
+  <si>
+    <t>TUERCA HEX H2 1/2 (SYC-12182)</t>
+  </si>
+  <si>
+    <t>PERNO HEX G-2 UNC ZN 1/2X11/2 (SYC-8179)</t>
+  </si>
+  <si>
+    <t>280 pend.</t>
+  </si>
+  <si>
+    <t>TUERCA HEX G-2 UNC ZN 1/2" (SYC-490)</t>
+  </si>
+  <si>
+    <t>PERNO HEX G-2 UNC 1/2 x 11/2 ZINCADO (SYC-8167)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0;[Red]&quot;$&quot;\-#,##0"/>
+    <numFmt numFmtId="169" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
+  </numFmts>
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -256,8 +670,53 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Montserrat Regular"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Montserrat Regular"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF030712"/>
+      <name val="Montserrat Regular"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF030712"/>
+      <name val="Montserrat Regular"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Montserrat Regular"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -276,6 +735,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -289,7 +754,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -299,6 +764,24 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="6" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -314,6 +797,582 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gonzalo Sepúlveda Iturra" refreshedDate="46100.802646759257" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="51" xr:uid="{138BA58F-E635-8A4B-9CCC-DD7C7FFEFA7D}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="H2:L53" sheet="GD 1972-1960-1959"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="DescGD" numFmtId="0">
+      <sharedItems count="25">
+        <s v="Tuerca Hexagonal Grado 2 1/2 NR"/>
+        <s v="Golilla Plana 1/2 NR"/>
+        <s v="Golilla Presión 1/2 NR"/>
+        <s v="Perno Hexagonal Grado 2 1/2 x 1.1/2 NR"/>
+        <s v="Perno Hexagonal Grado 2 1/2 x 2 NR"/>
+        <s v="Perno Hexagonal Grado 2 1/4 x 1 NR"/>
+        <s v="Perno Hexagonal A325 3/4 x 2.1/2 NR"/>
+        <s v="Perno Hexagonal Grado 2 3/8 x 1.1/2 NR"/>
+        <s v="Perno Hexagonal Grado 2 3/8 x 1 NR"/>
+        <s v="Perno Hexagonal Grado 2 3/8 X 3/4&quot; NR"/>
+        <s v="Perno Hexagonal Grado 2 5/8 x 4 NR"/>
+        <s v="Tuerca Hexagonal Grado 2 1/2 NR ​"/>
+        <s v="Tuerca Hexagonal Grado 2 1/4 NR"/>
+        <s v="Tuerca Hexagonal Grado 2 3/4 NR"/>
+        <s v="Tuerca Hexagonal Grado 2 3/8 NR"/>
+        <s v="Tuerca Hexagonal Grado 2 5/8 NR"/>
+        <s v="Golilla Plana 1/4 NR"/>
+        <s v="Golilla Plana 3/8 NR"/>
+        <s v="Golilla Plana 5/8 NR"/>
+        <s v="Golilla Presión 1/4 NR"/>
+        <s v="Golilla Presión 3/4 NR"/>
+        <s v="Golilla Presión 3/8 NR"/>
+        <s v="Golilla Presión 5/8 NR"/>
+        <s v="Golilla Plana 3/4 NR"/>
+        <s v="Perno Hexagonal Grado 2 1/2X1 Pulg ​"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="CANTIDAD" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="4" maxValue="1520"/>
+    </cacheField>
+    <cacheField name="UNIDAD" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="PRECIO UNITARIO" numFmtId="169">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="6" maxValue="1008"/>
+    </cacheField>
+    <cacheField name="TOTAL" numFmtId="169">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="100" maxValue="81312"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="51">
+  <r>
+    <x v="0"/>
+    <n v="616"/>
+    <s v="UN"/>
+    <n v="45"/>
+    <n v="27720"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="616"/>
+    <s v="UN"/>
+    <n v="25"/>
+    <n v="15400"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="616"/>
+    <s v="UN"/>
+    <n v="26"/>
+    <n v="16016"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="120"/>
+    <s v="UN"/>
+    <n v="132"/>
+    <n v="15840"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="120"/>
+    <s v="UN"/>
+    <n v="45"/>
+    <n v="5400"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="120"/>
+    <s v="UN"/>
+    <n v="25"/>
+    <n v="3000"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="120"/>
+    <s v="UN"/>
+    <n v="26"/>
+    <n v="3120"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="20"/>
+    <s v="UN"/>
+    <n v="171"/>
+    <n v="3420"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="20"/>
+    <s v="UN"/>
+    <n v="25"/>
+    <n v="500"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="20"/>
+    <s v="UN"/>
+    <n v="26"/>
+    <n v="520"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="20"/>
+    <s v="UN"/>
+    <n v="45"/>
+    <n v="900"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="40"/>
+    <s v="UN"/>
+    <n v="18"/>
+    <n v="720"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="80"/>
+    <s v="UN"/>
+    <n v="1008"/>
+    <n v="80640"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="140"/>
+    <s v="UN"/>
+    <n v="68"/>
+    <n v="9520"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="208"/>
+    <s v="UN"/>
+    <n v="54"/>
+    <n v="11232"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="60"/>
+    <s v="UN"/>
+    <n v="58"/>
+    <n v="3480"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="120"/>
+    <s v="UN"/>
+    <n v="68"/>
+    <n v="8160"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="56"/>
+    <s v="UN"/>
+    <n v="445"/>
+    <n v="24920"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <n v="1520"/>
+    <s v="UN"/>
+    <n v="42"/>
+    <n v="63840"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <n v="40"/>
+    <s v="UN"/>
+    <n v="38"/>
+    <n v="1520"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <n v="80"/>
+    <s v="UN"/>
+    <n v="251"/>
+    <n v="20080"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <n v="180"/>
+    <s v="UN"/>
+    <n v="22"/>
+    <n v="3960"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <n v="348"/>
+    <s v="UN"/>
+    <n v="22"/>
+    <n v="7656"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <n v="56"/>
+    <s v="UN"/>
+    <n v="88"/>
+    <n v="4928"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <n v="156"/>
+    <s v="UN"/>
+    <n v="88"/>
+    <n v="13728"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <n v="40"/>
+    <s v="UN"/>
+    <n v="8"/>
+    <n v="320"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <n v="208"/>
+    <s v="UN"/>
+    <n v="11"/>
+    <n v="2288"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <n v="56"/>
+    <s v="UN"/>
+    <n v="32"/>
+    <n v="1792"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="120"/>
+    <s v="UN"/>
+    <n v="26"/>
+    <n v="3120"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1400"/>
+    <s v="UN"/>
+    <n v="26"/>
+    <n v="36400"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <n v="40"/>
+    <s v="UN"/>
+    <n v="6"/>
+    <n v="240"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <n v="80"/>
+    <s v="UN"/>
+    <n v="66"/>
+    <n v="5280"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <n v="320"/>
+    <s v="UN"/>
+    <n v="9"/>
+    <n v="2880"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <n v="208"/>
+    <s v="UN"/>
+    <n v="9"/>
+    <n v="1872"/>
+  </r>
+  <r>
+    <x v="22"/>
+    <n v="156"/>
+    <s v="UN"/>
+    <n v="21"/>
+    <n v="3276"/>
+  </r>
+  <r>
+    <x v="22"/>
+    <n v="56"/>
+    <s v="UN"/>
+    <n v="21"/>
+    <n v="1176"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="120"/>
+    <s v="UN"/>
+    <n v="25"/>
+    <n v="3000"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="156"/>
+    <s v="UN"/>
+    <n v="25"/>
+    <n v="3900"/>
+  </r>
+  <r>
+    <x v="23"/>
+    <n v="80"/>
+    <s v="UN"/>
+    <n v="60"/>
+    <n v="4800"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <n v="320"/>
+    <s v="UN"/>
+    <n v="11"/>
+    <n v="3520"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <n v="156"/>
+    <s v="UN"/>
+    <n v="32"/>
+    <n v="4992"/>
+  </r>
+  <r>
+    <x v="24"/>
+    <n v="268"/>
+    <s v="UN"/>
+    <n v="103"/>
+    <n v="27604"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="UN"/>
+    <n v="132"/>
+    <n v="528"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="4"/>
+    <s v="UN"/>
+    <n v="25"/>
+    <n v="100"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="4"/>
+    <s v="UN"/>
+    <n v="26"/>
+    <n v="104"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="4"/>
+    <s v="UN"/>
+    <n v="45"/>
+    <n v="180"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="280"/>
+    <s v="UN"/>
+    <n v="132"/>
+    <n v="36960"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="280"/>
+    <s v="UN"/>
+    <n v="25"/>
+    <n v="7000"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="280"/>
+    <s v="UN"/>
+    <n v="26"/>
+    <n v="7280"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="280"/>
+    <s v="UN"/>
+    <n v="45"/>
+    <n v="12600"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="616"/>
+    <s v="UN"/>
+    <n v="132"/>
+    <n v="81312"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1C90A5F9-78EF-1341-B260-AD3F4D885203}" name="TablaDinámica2" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="N2:P28" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="26">
+        <item x="1"/>
+        <item x="16"/>
+        <item x="23"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="2"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="24"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="169" showAll="0"/>
+    <pivotField dataField="1" numFmtId="169" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="26">
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Suma de TOTAL" fld="4" baseField="0" baseItem="0" numFmtId="169"/>
+    <dataField name="Promedio de PRECIO UNITARIO" fld="3" subtotal="average" baseField="0" baseItem="0" numFmtId="169"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -637,14 +1696,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="64.28515625" customWidth="1"/>
     <col min="3" max="3" width="35.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>23</v>
       </c>
@@ -655,7 +1714,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="20">
       <c r="C2" s="4">
         <v>1815</v>
       </c>
@@ -666,7 +1725,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="20">
       <c r="C3" s="4">
         <v>1905</v>
       </c>
@@ -677,7 +1736,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="20">
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="F4" s="6" t="s">
@@ -690,7 +1749,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="20">
       <c r="C5" s="4">
         <v>1966</v>
       </c>
@@ -701,7 +1760,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="20">
       <c r="C6" s="2">
         <v>1974</v>
       </c>
@@ -718,7 +1777,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="20">
       <c r="C7" s="2">
         <v>1981</v>
       </c>
@@ -735,7 +1794,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="20">
       <c r="C8" s="4">
         <v>1982</v>
       </c>
@@ -746,7 +1805,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="20">
       <c r="C9" s="4">
         <v>1983</v>
       </c>
@@ -757,7 +1816,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="20">
       <c r="C10" s="4">
         <v>1986</v>
       </c>
@@ -768,7 +1827,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="20">
       <c r="C11" s="2">
         <v>1987</v>
       </c>
@@ -785,7 +1844,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="20">
       <c r="C12" s="2">
         <v>1989</v>
       </c>
@@ -802,7 +1861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="20">
       <c r="C13" s="2">
         <v>1990</v>
       </c>
@@ -819,7 +1878,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="20">
       <c r="C14" s="2">
         <v>1991</v>
       </c>
@@ -836,7 +1895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="20">
       <c r="C15" s="2">
         <v>1992</v>
       </c>
@@ -853,7 +1912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="20">
       <c r="C16" s="2">
         <v>1993</v>
       </c>
@@ -870,7 +1929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="20" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="20">
       <c r="C17" s="2">
         <v>1994</v>
       </c>
@@ -887,42 +1946,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" ht="18">
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="18">
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
     </row>
-    <row r="20" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" ht="18">
       <c r="A20" t="s">
         <v>24</v>
       </c>
       <c r="D20" s="1"/>
     </row>
-    <row r="21" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" ht="18">
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" ht="18">
       <c r="A22" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" ht="18">
       <c r="D23" s="1"/>
     </row>
-    <row r="24" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" ht="18">
       <c r="A24" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" ht="18">
       <c r="D25" s="1"/>
     </row>
-    <row r="26" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" ht="18">
       <c r="A26" s="7" t="s">
         <v>27</v>
       </c>
@@ -934,7 +1993,7 @@
       </c>
       <c r="D26" s="1"/>
     </row>
-    <row r="27" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" ht="18">
       <c r="A27" s="7">
         <v>1815</v>
       </c>
@@ -946,7 +2005,7 @@
       </c>
       <c r="D27" s="1"/>
     </row>
-    <row r="28" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" ht="18">
       <c r="A28" s="7">
         <v>1905</v>
       </c>
@@ -958,7 +2017,7 @@
       </c>
       <c r="D28" s="1"/>
     </row>
-    <row r="29" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" ht="18">
       <c r="A29" s="7">
         <v>1966</v>
       </c>
@@ -970,7 +2029,7 @@
       </c>
       <c r="D29" s="1"/>
     </row>
-    <row r="30" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" ht="18">
       <c r="A30" s="7">
         <v>1982</v>
       </c>
@@ -982,7 +2041,7 @@
       </c>
       <c r="D30" s="1"/>
     </row>
-    <row r="31" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" ht="18">
       <c r="A31" s="7">
         <v>1983</v>
       </c>
@@ -994,7 +2053,7 @@
       </c>
       <c r="D31" s="1"/>
     </row>
-    <row r="32" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" ht="18">
       <c r="A32" s="7">
         <v>1986</v>
       </c>
@@ -1006,32 +2065,32 @@
       </c>
       <c r="D32" s="1"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1">
       <c r="A34" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1">
       <c r="A36" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1">
       <c r="A38" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1">
       <c r="A39" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1">
       <c r="A40" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -1043,4 +2102,2916 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="89" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07ED76D3-9DCD-AF46-93A0-3260D7DD697E}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:X53"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="5" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" style="9"/>
+    <col min="3" max="3" width="32.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" style="9"/>
+    <col min="5" max="5" width="12.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="9"/>
+    <col min="7" max="7" width="35.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" style="9"/>
+    <col min="14" max="14" width="32.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" style="9"/>
+    <col min="18" max="18" width="39.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="49" style="9" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6" style="9" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="2" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="10.7109375" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24">
+      <c r="A1" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="19">
+        <f>+SUBTOTAL(9,D3:D30)</f>
+        <v>1248</v>
+      </c>
+      <c r="E1" s="19">
+        <f>+SUBTOTAL(9,E3:E30)</f>
+        <v>58032</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="19">
+        <f>+SUBTOTAL(9,I3:I53)</f>
+        <v>276</v>
+      </c>
+      <c r="L1" s="19">
+        <f>+SUBTOTAL(9,L3:L53)</f>
+        <v>19248</v>
+      </c>
+      <c r="U1" s="19">
+        <f>+SUBTOTAL(9,U2:U52)</f>
+        <v>528</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" hidden="1">
+      <c r="A2" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="O2" t="s">
+        <v>120</v>
+      </c>
+      <c r="P2" t="s">
+        <v>118</v>
+      </c>
+      <c r="R2" s="20" t="str">
+        <f>+VLOOKUP(T2,$B$3:$E$30,2,FALSE)</f>
+        <v>Tuerca Hexagonal Grado 2 1/2 NR</v>
+      </c>
+      <c r="S2" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="T2" s="22">
+        <v>45</v>
+      </c>
+      <c r="U2" s="21">
+        <v>616</v>
+      </c>
+      <c r="V2" s="21">
+        <v>0</v>
+      </c>
+      <c r="W2" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="X2" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" hidden="1">
+      <c r="A3" s="9">
+        <v>1959</v>
+      </c>
+      <c r="B3" s="13">
+        <v>88</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="13">
+        <v>212</v>
+      </c>
+      <c r="E3" s="13">
+        <v>18656</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I3" s="12">
+        <v>616</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" s="15">
+        <v>25</v>
+      </c>
+      <c r="L3" s="15">
+        <v>15400</v>
+      </c>
+      <c r="N3" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="O3" s="18">
+        <v>240</v>
+      </c>
+      <c r="P3" s="18">
+        <v>6</v>
+      </c>
+      <c r="R3" s="20" t="str">
+        <f t="shared" ref="R3:R52" si="0">+VLOOKUP(T3,$B$3:$E$30,2,FALSE)</f>
+        <v>Golilla Plana 1/2 NR</v>
+      </c>
+      <c r="S3" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="T3" s="22">
+        <v>25</v>
+      </c>
+      <c r="U3" s="21">
+        <v>616</v>
+      </c>
+      <c r="V3" s="21">
+        <v>0</v>
+      </c>
+      <c r="W3" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="X3" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" hidden="1">
+      <c r="A4" s="9">
+        <v>1959</v>
+      </c>
+      <c r="B4" s="13">
+        <v>6</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="13">
+        <v>40</v>
+      </c>
+      <c r="E4" s="13">
+        <v>240</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I4" s="12">
+        <v>120</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K4" s="15">
+        <v>25</v>
+      </c>
+      <c r="L4" s="15">
+        <v>3000</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="O4" s="18">
+        <v>320</v>
+      </c>
+      <c r="P4" s="18">
+        <v>8</v>
+      </c>
+      <c r="R4" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Presión 1/2 NR</v>
+      </c>
+      <c r="S4" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="T4" s="22">
+        <v>26</v>
+      </c>
+      <c r="U4" s="21">
+        <v>616</v>
+      </c>
+      <c r="V4" s="21">
+        <v>0</v>
+      </c>
+      <c r="W4" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="X4" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" hidden="1">
+      <c r="A5" s="9">
+        <v>1959</v>
+      </c>
+      <c r="B5" s="13">
+        <v>21</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="13">
+        <v>212</v>
+      </c>
+      <c r="E5" s="13">
+        <v>4452</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I5" s="12">
+        <v>20</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K5" s="15">
+        <v>25</v>
+      </c>
+      <c r="L5" s="15">
+        <v>500</v>
+      </c>
+      <c r="N5" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="O5" s="18">
+        <v>4752</v>
+      </c>
+      <c r="P5" s="18">
+        <v>9</v>
+      </c>
+      <c r="R5" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Perno Hexagonal Grado 2 1/2 x 1.1/2 NR ​</v>
+      </c>
+      <c r="S5" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="T5" s="22">
+        <v>132</v>
+      </c>
+      <c r="U5" s="21">
+        <v>120</v>
+      </c>
+      <c r="V5" s="21">
+        <v>0</v>
+      </c>
+      <c r="W5" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="X5" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" hidden="1">
+      <c r="A6" s="9">
+        <v>1972</v>
+      </c>
+      <c r="B6" s="13">
+        <v>132</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="13">
+        <v>520</v>
+      </c>
+      <c r="E6" s="13">
+        <v>68640</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" s="12">
+        <v>120</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K6" s="15">
+        <v>25</v>
+      </c>
+      <c r="L6" s="15">
+        <v>3000</v>
+      </c>
+      <c r="N6" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="O6" s="18">
+        <v>5808</v>
+      </c>
+      <c r="P6" s="18">
+        <v>11</v>
+      </c>
+      <c r="R6" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Tuerca Hexagonal Grado 2 1/2 NR</v>
+      </c>
+      <c r="S6" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="T6" s="22">
+        <v>45</v>
+      </c>
+      <c r="U6" s="21">
+        <v>120</v>
+      </c>
+      <c r="V6" s="21">
+        <v>0</v>
+      </c>
+      <c r="W6" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="X6" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" hidden="1">
+      <c r="A7" s="9">
+        <v>1972</v>
+      </c>
+      <c r="B7" s="13">
+        <v>42</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="13">
+        <v>1520</v>
+      </c>
+      <c r="E7" s="13">
+        <v>63840</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I7" s="12">
+        <v>156</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K7" s="15">
+        <v>25</v>
+      </c>
+      <c r="L7" s="15">
+        <v>3900</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="O7" s="18">
+        <v>720</v>
+      </c>
+      <c r="P7" s="18">
+        <v>18</v>
+      </c>
+      <c r="R7" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Plana 1/2 NR</v>
+      </c>
+      <c r="S7" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="T7" s="22">
+        <v>25</v>
+      </c>
+      <c r="U7" s="21">
+        <v>120</v>
+      </c>
+      <c r="V7" s="21">
+        <v>0</v>
+      </c>
+      <c r="W7" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="X7" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" hidden="1">
+      <c r="A8" s="9">
+        <v>1972</v>
+      </c>
+      <c r="B8" s="13">
+        <v>103</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="13">
+        <v>268</v>
+      </c>
+      <c r="E8" s="13">
+        <v>27604</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I8" s="12">
+        <v>4</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K8" s="15">
+        <v>25</v>
+      </c>
+      <c r="L8" s="15">
+        <v>100</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="O8" s="18">
+        <v>4452</v>
+      </c>
+      <c r="P8" s="18">
+        <v>21</v>
+      </c>
+      <c r="R8" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Presión 1/2 NR</v>
+      </c>
+      <c r="S8" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="T8" s="22">
+        <v>26</v>
+      </c>
+      <c r="U8" s="21">
+        <v>120</v>
+      </c>
+      <c r="V8" s="21">
+        <v>0</v>
+      </c>
+      <c r="W8" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="X8" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" hidden="1">
+      <c r="A9" s="9">
+        <v>1959</v>
+      </c>
+      <c r="B9" s="13">
+        <v>8</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="13">
+        <v>40</v>
+      </c>
+      <c r="E9" s="13">
+        <v>320</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" s="12">
+        <v>280</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K9" s="15">
+        <v>25</v>
+      </c>
+      <c r="L9" s="15">
+        <v>7000</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="O9" s="18">
+        <v>11616</v>
+      </c>
+      <c r="P9" s="18">
+        <v>22</v>
+      </c>
+      <c r="R9" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Perno Hexagonal Grado 2 1/2 x 2 NR</v>
+      </c>
+      <c r="S9" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="T9" s="22">
+        <v>171</v>
+      </c>
+      <c r="U9" s="21">
+        <v>20</v>
+      </c>
+      <c r="V9" s="21">
+        <v>0</v>
+      </c>
+      <c r="W9" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="X9" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" hidden="1">
+      <c r="A10" s="9">
+        <v>1959</v>
+      </c>
+      <c r="B10" s="13">
+        <v>66</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="13">
+        <v>80</v>
+      </c>
+      <c r="E10" s="13">
+        <v>5280</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="12">
+        <v>40</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" s="15">
+        <v>8</v>
+      </c>
+      <c r="L10" s="15">
+        <v>320</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="O10" s="18">
+        <v>32900</v>
+      </c>
+      <c r="P10" s="18">
+        <v>25</v>
+      </c>
+      <c r="R10" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Plana 1/2 NR</v>
+      </c>
+      <c r="S10" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="T10" s="22">
+        <v>25</v>
+      </c>
+      <c r="U10" s="21">
+        <v>20</v>
+      </c>
+      <c r="V10" s="21">
+        <v>0</v>
+      </c>
+      <c r="W10" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="X10" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" hidden="1">
+      <c r="A11" s="9">
+        <v>1959</v>
+      </c>
+      <c r="B11" s="13">
+        <v>60</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="13">
+        <v>80</v>
+      </c>
+      <c r="E11" s="13">
+        <v>4800</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="12">
+        <v>80</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K11" s="15">
+        <v>60</v>
+      </c>
+      <c r="L11" s="15">
+        <v>4800</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="O11" s="18">
+        <v>66560</v>
+      </c>
+      <c r="P11" s="18">
+        <v>26</v>
+      </c>
+      <c r="R11" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Presión 1/2 NR</v>
+      </c>
+      <c r="S11" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="T11" s="22">
+        <v>26</v>
+      </c>
+      <c r="U11" s="21">
+        <v>20</v>
+      </c>
+      <c r="V11" s="21">
+        <v>0</v>
+      </c>
+      <c r="W11" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="X11" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" hidden="1">
+      <c r="A12" s="9">
+        <v>1960</v>
+      </c>
+      <c r="B12" s="13">
+        <v>26</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="13">
+        <v>1520</v>
+      </c>
+      <c r="E12" s="13">
+        <v>39520</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" s="12">
+        <v>208</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K12" s="15">
+        <v>11</v>
+      </c>
+      <c r="L12" s="15">
+        <v>2288</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="O12" s="18">
+        <v>6784</v>
+      </c>
+      <c r="P12" s="18">
+        <v>32</v>
+      </c>
+      <c r="R12" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Tuerca Hexagonal Grado 2 1/2 NR</v>
+      </c>
+      <c r="S12" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="T12" s="22">
+        <v>45</v>
+      </c>
+      <c r="U12" s="21">
+        <v>20</v>
+      </c>
+      <c r="V12" s="21">
+        <v>0</v>
+      </c>
+      <c r="W12" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="X12" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" hidden="1">
+      <c r="A13" s="9">
+        <v>1959</v>
+      </c>
+      <c r="B13" s="13">
+        <v>11</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="13">
+        <v>528</v>
+      </c>
+      <c r="E13" s="13">
+        <v>5808</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="12">
+        <v>320</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K13" s="15">
+        <v>11</v>
+      </c>
+      <c r="L13" s="15">
+        <v>3520</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="O13" s="18">
+        <v>1520</v>
+      </c>
+      <c r="P13" s="18">
+        <v>38</v>
+      </c>
+      <c r="R13" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Perno Hexagonal Grado 2 1/4 x 1 NR</v>
+      </c>
+      <c r="S13" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="T13" s="22">
+        <v>18</v>
+      </c>
+      <c r="U13" s="21">
+        <v>40</v>
+      </c>
+      <c r="V13" s="21">
+        <v>0</v>
+      </c>
+      <c r="W13" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="X13" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" hidden="1">
+      <c r="A14" s="9">
+        <v>1959</v>
+      </c>
+      <c r="B14" s="13">
+        <v>9</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="13">
+        <v>528</v>
+      </c>
+      <c r="E14" s="13">
+        <v>4752</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="I14" s="12">
+        <v>56</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K14" s="15">
+        <v>32</v>
+      </c>
+      <c r="L14" s="15">
+        <v>1792</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="O14" s="18">
+        <v>63840</v>
+      </c>
+      <c r="P14" s="18">
+        <v>42</v>
+      </c>
+      <c r="R14" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Perno Hexagonal A325 3/4 x 2.1/2 NR</v>
+      </c>
+      <c r="S14" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="T14" s="22">
+        <v>1008</v>
+      </c>
+      <c r="U14" s="21">
+        <v>80</v>
+      </c>
+      <c r="V14" s="21">
+        <v>0</v>
+      </c>
+      <c r="W14" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="X14" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" hidden="1">
+      <c r="A15" s="9">
+        <v>1960</v>
+      </c>
+      <c r="B15" s="13">
+        <v>25</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="13">
+        <v>276</v>
+      </c>
+      <c r="E15" s="13">
+        <v>6900</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="I15" s="12">
+        <v>156</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K15" s="15">
+        <v>32</v>
+      </c>
+      <c r="L15" s="15">
+        <v>4992</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="O15" s="18">
+        <v>46800</v>
+      </c>
+      <c r="P15" s="18">
+        <v>45</v>
+      </c>
+      <c r="R15" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Perno Hexagonal Grado 2 3/8 x 1.1/2 NR</v>
+      </c>
+      <c r="S15" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="T15" s="22">
+        <v>68</v>
+      </c>
+      <c r="U15" s="21">
+        <v>140</v>
+      </c>
+      <c r="V15" s="21">
+        <v>0</v>
+      </c>
+      <c r="W15" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="X15" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" hidden="1">
+      <c r="A16" s="9">
+        <v>1960</v>
+      </c>
+      <c r="B16" s="13">
+        <v>171</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="13">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13">
+        <v>3420</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="I16" s="12">
+        <v>616</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K16" s="15">
+        <v>26</v>
+      </c>
+      <c r="L16" s="15">
+        <v>16016</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="O16" s="18">
+        <v>11232</v>
+      </c>
+      <c r="P16" s="18">
+        <v>54</v>
+      </c>
+      <c r="R16" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Perno Hexagonal Grado 2 3/8 x 1 NR</v>
+      </c>
+      <c r="S16" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="T16" s="22">
+        <v>54</v>
+      </c>
+      <c r="U16" s="21">
+        <v>208</v>
+      </c>
+      <c r="V16" s="21">
+        <v>0</v>
+      </c>
+      <c r="W16" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="X16" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" hidden="1">
+      <c r="A17" s="9">
+        <v>1960</v>
+      </c>
+      <c r="B17" s="13">
+        <v>132</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="13">
+        <v>500</v>
+      </c>
+      <c r="E17" s="13">
+        <v>66000</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="I17" s="12">
+        <v>120</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K17" s="15">
+        <v>26</v>
+      </c>
+      <c r="L17" s="15">
+        <v>3120</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="O17" s="18">
+        <v>3480</v>
+      </c>
+      <c r="P17" s="18">
+        <v>58</v>
+      </c>
+      <c r="R17" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Perno Hexagonal Grado 2 3/8 X 3/4" NR</v>
+      </c>
+      <c r="S17" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="T17" s="22">
+        <v>58</v>
+      </c>
+      <c r="U17" s="21">
+        <v>60</v>
+      </c>
+      <c r="V17" s="21">
+        <v>0</v>
+      </c>
+      <c r="W17" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="X17" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" hidden="1">
+      <c r="A18" s="9">
+        <v>1960</v>
+      </c>
+      <c r="B18" s="13">
+        <v>1008</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="13">
+        <v>80</v>
+      </c>
+      <c r="E18" s="13">
+        <v>80640</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="I18" s="12">
+        <v>20</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K18" s="15">
+        <v>26</v>
+      </c>
+      <c r="L18" s="15">
+        <v>520</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="O18" s="18">
+        <v>4800</v>
+      </c>
+      <c r="P18" s="18">
+        <v>60</v>
+      </c>
+      <c r="R18" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Perno Hexagonal Grado 2 3/8 x 1.1/2 NR</v>
+      </c>
+      <c r="S18" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="T18" s="22">
+        <v>68</v>
+      </c>
+      <c r="U18" s="21">
+        <v>120</v>
+      </c>
+      <c r="V18" s="21">
+        <v>0</v>
+      </c>
+      <c r="W18" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="X18" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" hidden="1">
+      <c r="A19" s="9">
+        <v>1960</v>
+      </c>
+      <c r="B19" s="13">
+        <v>18</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="13">
+        <v>40</v>
+      </c>
+      <c r="E19" s="13">
+        <v>720</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="I19" s="12">
+        <v>120</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K19" s="15">
+        <v>26</v>
+      </c>
+      <c r="L19" s="15">
+        <v>3120</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="O19" s="18">
+        <v>5280</v>
+      </c>
+      <c r="P19" s="18">
+        <v>66</v>
+      </c>
+      <c r="R19" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Perno Hexagonal Grado 2 5/8 x 4 NR</v>
+      </c>
+      <c r="S19" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="T19" s="22">
+        <v>445</v>
+      </c>
+      <c r="U19" s="21">
+        <v>56</v>
+      </c>
+      <c r="V19" s="21">
+        <v>0</v>
+      </c>
+      <c r="W19" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="X19" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" hidden="1">
+      <c r="A20" s="9">
+        <v>1960</v>
+      </c>
+      <c r="B20" s="13">
+        <v>68</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="13">
+        <v>260</v>
+      </c>
+      <c r="E20" s="13">
+        <v>17680</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="I20" s="12">
+        <v>1400</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K20" s="15">
+        <v>26</v>
+      </c>
+      <c r="L20" s="15">
+        <v>36400</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="O20" s="18">
+        <v>17680</v>
+      </c>
+      <c r="P20" s="18">
+        <v>68</v>
+      </c>
+      <c r="R20" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Tuerca Hexagonal Grado 2 1/2 NR ​</v>
+      </c>
+      <c r="S20" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="T20" s="22">
+        <v>42</v>
+      </c>
+      <c r="U20" s="24">
+        <v>1520</v>
+      </c>
+      <c r="V20" s="21">
+        <v>0</v>
+      </c>
+      <c r="W20" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="X20" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" hidden="1">
+      <c r="A21" s="9">
+        <v>1959</v>
+      </c>
+      <c r="B21" s="13">
+        <v>22</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="13">
+        <v>528</v>
+      </c>
+      <c r="E21" s="13">
+        <v>11616</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="I21" s="12">
+        <v>4</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K21" s="15">
+        <v>26</v>
+      </c>
+      <c r="L21" s="15">
+        <v>104</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="O21" s="18">
+        <v>18656</v>
+      </c>
+      <c r="P21" s="18">
+        <v>88</v>
+      </c>
+      <c r="R21" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Tuerca Hexagonal Grado 2 1/4 NR</v>
+      </c>
+      <c r="S21" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="T21" s="22">
+        <v>38</v>
+      </c>
+      <c r="U21" s="21">
+        <v>40</v>
+      </c>
+      <c r="V21" s="21">
+        <v>0</v>
+      </c>
+      <c r="W21" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="X21" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" hidden="1">
+      <c r="A22" s="9">
+        <v>1959</v>
+      </c>
+      <c r="B22" s="13">
+        <v>32</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="13">
+        <v>212</v>
+      </c>
+      <c r="E22" s="13">
+        <v>6784</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="I22" s="12">
+        <v>280</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K22" s="15">
+        <v>26</v>
+      </c>
+      <c r="L22" s="15">
+        <v>7280</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="O22" s="18">
+        <v>27604</v>
+      </c>
+      <c r="P22" s="18">
+        <v>103</v>
+      </c>
+      <c r="R22" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Tuerca Hexagonal Grado 2 3/4 NR</v>
+      </c>
+      <c r="S22" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="T22" s="22">
+        <v>251</v>
+      </c>
+      <c r="U22" s="21">
+        <v>80</v>
+      </c>
+      <c r="V22" s="21">
+        <v>0</v>
+      </c>
+      <c r="W22" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="X22" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24">
+      <c r="A23" s="9">
+        <v>1960</v>
+      </c>
+      <c r="B23" s="13">
+        <v>45</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="13">
+        <v>1040</v>
+      </c>
+      <c r="E23" s="13">
+        <v>46800</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I23" s="12">
+        <v>40</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K23" s="15">
+        <v>6</v>
+      </c>
+      <c r="L23" s="15">
+        <v>240</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="O23" s="18">
+        <v>134640</v>
+      </c>
+      <c r="P23" s="18">
+        <v>132</v>
+      </c>
+      <c r="R23" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Tuerca Hexagonal Grado 2 3/8 NR</v>
+      </c>
+      <c r="S23" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="T23" s="22">
+        <v>22</v>
+      </c>
+      <c r="U23" s="21">
+        <v>180</v>
+      </c>
+      <c r="V23" s="21">
+        <v>0</v>
+      </c>
+      <c r="W23" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="X23" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24">
+      <c r="A24" s="9">
+        <v>1960</v>
+      </c>
+      <c r="B24" s="13">
+        <v>54</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" s="13">
+        <v>208</v>
+      </c>
+      <c r="E24" s="13">
+        <v>11232</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="I24" s="12">
+        <v>80</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K24" s="15">
+        <v>66</v>
+      </c>
+      <c r="L24" s="15">
+        <v>5280</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="O24" s="18">
+        <v>3420</v>
+      </c>
+      <c r="P24" s="18">
+        <v>171</v>
+      </c>
+      <c r="R24" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Tuerca Hexagonal Grado 2 3/8 NR</v>
+      </c>
+      <c r="S24" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="T24" s="22">
+        <v>22</v>
+      </c>
+      <c r="U24" s="21">
+        <v>348</v>
+      </c>
+      <c r="V24" s="21">
+        <v>0</v>
+      </c>
+      <c r="W24" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="X24" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" hidden="1">
+      <c r="A25" s="9">
+        <v>1960</v>
+      </c>
+      <c r="B25" s="13">
+        <v>58</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="13">
+        <v>60</v>
+      </c>
+      <c r="E25" s="13">
+        <v>3480</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="I25" s="12">
+        <v>320</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K25" s="15">
+        <v>9</v>
+      </c>
+      <c r="L25" s="15">
+        <v>2880</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="O25" s="18">
+        <v>20080</v>
+      </c>
+      <c r="P25" s="18">
+        <v>251</v>
+      </c>
+      <c r="R25" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Tuerca Hexagonal Grado 2 5/8 NR</v>
+      </c>
+      <c r="S25" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="T25" s="22">
+        <v>88</v>
+      </c>
+      <c r="U25" s="21">
+        <v>56</v>
+      </c>
+      <c r="V25" s="21">
+        <v>0</v>
+      </c>
+      <c r="W25" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="X25" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" hidden="1">
+      <c r="A26" s="9">
+        <v>1960</v>
+      </c>
+      <c r="B26" s="13">
+        <v>445</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" s="13">
+        <v>56</v>
+      </c>
+      <c r="E26" s="13">
+        <v>24920</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="I26" s="12">
+        <v>208</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K26" s="15">
+        <v>9</v>
+      </c>
+      <c r="L26" s="15">
+        <v>1872</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="O26" s="18">
+        <v>24920</v>
+      </c>
+      <c r="P26" s="18">
+        <v>445</v>
+      </c>
+      <c r="R26" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Tuerca Hexagonal Grado 2 5/8 NR</v>
+      </c>
+      <c r="S26" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="T26" s="22">
+        <v>88</v>
+      </c>
+      <c r="U26" s="21">
+        <v>156</v>
+      </c>
+      <c r="V26" s="21">
+        <v>0</v>
+      </c>
+      <c r="W26" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="X26" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" hidden="1">
+      <c r="A27" s="9">
+        <v>1960</v>
+      </c>
+      <c r="B27" s="13">
+        <v>38</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="13">
+        <v>40</v>
+      </c>
+      <c r="E27" s="13">
+        <v>1520</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="I27" s="12">
+        <v>156</v>
+      </c>
+      <c r="J27" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K27" s="15">
+        <v>21</v>
+      </c>
+      <c r="L27" s="15">
+        <v>3276</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="O27" s="18">
+        <v>80640</v>
+      </c>
+      <c r="P27" s="18">
+        <v>1008</v>
+      </c>
+      <c r="R27" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Plana 1/4 NR</v>
+      </c>
+      <c r="S27" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="T27" s="22">
+        <v>8</v>
+      </c>
+      <c r="U27" s="21">
+        <v>40</v>
+      </c>
+      <c r="V27" s="21">
+        <v>0</v>
+      </c>
+      <c r="W27" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="X27" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" hidden="1">
+      <c r="A28" s="9">
+        <v>1960</v>
+      </c>
+      <c r="B28" s="13">
+        <v>251</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" s="13">
+        <v>80</v>
+      </c>
+      <c r="E28" s="13">
+        <v>20080</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="I28" s="12">
+        <v>56</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K28" s="15">
+        <v>21</v>
+      </c>
+      <c r="L28" s="15">
+        <v>1176</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="O28" s="18">
+        <v>598744</v>
+      </c>
+      <c r="P28" s="18">
+        <v>77.254901960784309</v>
+      </c>
+      <c r="R28" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Plana 3/8 NR</v>
+      </c>
+      <c r="S28" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="T28" s="22">
+        <v>11</v>
+      </c>
+      <c r="U28" s="21">
+        <v>208</v>
+      </c>
+      <c r="V28" s="21">
+        <v>0</v>
+      </c>
+      <c r="W28" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="X28" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" hidden="1">
+      <c r="A29" s="9">
+        <v>1972</v>
+      </c>
+      <c r="B29" s="13">
+        <v>25</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="13">
+        <v>1040</v>
+      </c>
+      <c r="E29" s="13">
+        <v>26000</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="I29" s="12">
+        <v>80</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K29" s="15">
+        <v>1008</v>
+      </c>
+      <c r="L29" s="15">
+        <v>80640</v>
+      </c>
+      <c r="R29" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Plana 5/8 NR</v>
+      </c>
+      <c r="S29" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="T29" s="22">
+        <v>32</v>
+      </c>
+      <c r="U29" s="21">
+        <v>56</v>
+      </c>
+      <c r="V29" s="21">
+        <v>0</v>
+      </c>
+      <c r="W29" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="X29" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" hidden="1">
+      <c r="A30" s="9">
+        <v>1972</v>
+      </c>
+      <c r="B30" s="13">
+        <v>26</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" s="13">
+        <v>1040</v>
+      </c>
+      <c r="E30" s="13">
+        <v>27040</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="I30" s="12">
+        <v>120</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K30" s="15">
+        <v>132</v>
+      </c>
+      <c r="L30" s="15">
+        <v>15840</v>
+      </c>
+      <c r="R30" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Presión 1/2 NR</v>
+      </c>
+      <c r="S30" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="T30" s="22">
+        <v>26</v>
+      </c>
+      <c r="U30" s="21">
+        <v>120</v>
+      </c>
+      <c r="V30" s="21">
+        <v>0</v>
+      </c>
+      <c r="W30" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="X30" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" hidden="1">
+      <c r="G31" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="I31" s="12">
+        <v>4</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K31" s="15">
+        <v>132</v>
+      </c>
+      <c r="L31" s="15">
+        <v>528</v>
+      </c>
+      <c r="R31" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Presión 1/2 NR</v>
+      </c>
+      <c r="S31" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="T31" s="22">
+        <v>26</v>
+      </c>
+      <c r="U31" s="24">
+        <v>1400</v>
+      </c>
+      <c r="V31" s="21">
+        <v>0</v>
+      </c>
+      <c r="W31" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="X31" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" hidden="1">
+      <c r="G32" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="H32" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="I32" s="12">
+        <v>280</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K32" s="15">
+        <v>132</v>
+      </c>
+      <c r="L32" s="15">
+        <v>36960</v>
+      </c>
+      <c r="R32" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Presión 1/4 NR</v>
+      </c>
+      <c r="S32" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="T32" s="22">
+        <v>6</v>
+      </c>
+      <c r="U32" s="21">
+        <v>40</v>
+      </c>
+      <c r="V32" s="21">
+        <v>0</v>
+      </c>
+      <c r="W32" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="X32" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="7:24" hidden="1">
+      <c r="G33" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="H33" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="I33" s="12">
+        <v>616</v>
+      </c>
+      <c r="J33" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K33" s="15">
+        <v>132</v>
+      </c>
+      <c r="L33" s="15">
+        <v>81312</v>
+      </c>
+      <c r="R33" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Presión 3/4 NR</v>
+      </c>
+      <c r="S33" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="T33" s="22">
+        <v>66</v>
+      </c>
+      <c r="U33" s="21">
+        <v>80</v>
+      </c>
+      <c r="V33" s="21">
+        <v>0</v>
+      </c>
+      <c r="W33" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="X33" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="7:24" hidden="1">
+      <c r="G34" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="H34" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="I34" s="12">
+        <v>20</v>
+      </c>
+      <c r="J34" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K34" s="15">
+        <v>171</v>
+      </c>
+      <c r="L34" s="15">
+        <v>3420</v>
+      </c>
+      <c r="R34" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Presión 3/8 NR</v>
+      </c>
+      <c r="S34" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="T34" s="22">
+        <v>9</v>
+      </c>
+      <c r="U34" s="21">
+        <v>320</v>
+      </c>
+      <c r="V34" s="21">
+        <v>0</v>
+      </c>
+      <c r="W34" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="X34" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="7:24" hidden="1">
+      <c r="G35" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I35" s="12">
+        <v>268</v>
+      </c>
+      <c r="J35" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K35" s="15">
+        <v>103</v>
+      </c>
+      <c r="L35" s="15">
+        <v>27604</v>
+      </c>
+      <c r="R35" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Presión 3/8 NR</v>
+      </c>
+      <c r="S35" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="T35" s="22">
+        <v>9</v>
+      </c>
+      <c r="U35" s="21">
+        <v>208</v>
+      </c>
+      <c r="V35" s="21">
+        <v>0</v>
+      </c>
+      <c r="W35" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="X35" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="7:24" hidden="1">
+      <c r="G36" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I36" s="12">
+        <v>40</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K36" s="15">
+        <v>18</v>
+      </c>
+      <c r="L36" s="15">
+        <v>720</v>
+      </c>
+      <c r="R36" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Presión 5/8 NR</v>
+      </c>
+      <c r="S36" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="T36" s="22">
+        <v>21</v>
+      </c>
+      <c r="U36" s="21">
+        <v>156</v>
+      </c>
+      <c r="V36" s="21">
+        <v>0</v>
+      </c>
+      <c r="W36" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="X36" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="7:24" hidden="1">
+      <c r="G37" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="I37" s="12">
+        <v>208</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K37" s="15">
+        <v>54</v>
+      </c>
+      <c r="L37" s="15">
+        <v>11232</v>
+      </c>
+      <c r="R37" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Presión 5/8 NR</v>
+      </c>
+      <c r="S37" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="T37" s="22">
+        <v>21</v>
+      </c>
+      <c r="U37" s="21">
+        <v>56</v>
+      </c>
+      <c r="V37" s="21">
+        <v>0</v>
+      </c>
+      <c r="W37" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="X37" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="7:24" hidden="1">
+      <c r="G38" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="I38" s="12">
+        <v>140</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K38" s="15">
+        <v>68</v>
+      </c>
+      <c r="L38" s="15">
+        <v>9520</v>
+      </c>
+      <c r="R38" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Plana 1/2 NR</v>
+      </c>
+      <c r="S38" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="T38" s="22">
+        <v>25</v>
+      </c>
+      <c r="U38" s="21">
+        <v>120</v>
+      </c>
+      <c r="V38" s="21">
+        <v>0</v>
+      </c>
+      <c r="W38" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="X38" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="7:24" hidden="1">
+      <c r="G39" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="H39" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="I39" s="12">
+        <v>120</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K39" s="15">
+        <v>68</v>
+      </c>
+      <c r="L39" s="15">
+        <v>8160</v>
+      </c>
+      <c r="R39" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Plana 1/2 NR</v>
+      </c>
+      <c r="S39" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="T39" s="22">
+        <v>25</v>
+      </c>
+      <c r="U39" s="21">
+        <v>156</v>
+      </c>
+      <c r="V39" s="21">
+        <v>0</v>
+      </c>
+      <c r="W39" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="X39" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="7:24" hidden="1">
+      <c r="G40" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="H40" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I40" s="12">
+        <v>60</v>
+      </c>
+      <c r="J40" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K40" s="15">
+        <v>58</v>
+      </c>
+      <c r="L40" s="15">
+        <v>3480</v>
+      </c>
+      <c r="R40" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Plana 3/4 NR</v>
+      </c>
+      <c r="S40" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="T40" s="22">
+        <v>60</v>
+      </c>
+      <c r="U40" s="21">
+        <v>80</v>
+      </c>
+      <c r="V40" s="21">
+        <v>0</v>
+      </c>
+      <c r="W40" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="X40" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="7:24" hidden="1">
+      <c r="G41" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="H41" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="I41" s="12">
+        <v>56</v>
+      </c>
+      <c r="J41" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K41" s="15">
+        <v>445</v>
+      </c>
+      <c r="L41" s="15">
+        <v>24920</v>
+      </c>
+      <c r="R41" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Plana 3/8 NR</v>
+      </c>
+      <c r="S41" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="T41" s="22">
+        <v>11</v>
+      </c>
+      <c r="U41" s="21">
+        <v>320</v>
+      </c>
+      <c r="V41" s="21">
+        <v>0</v>
+      </c>
+      <c r="W41" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="X41" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="7:24" hidden="1">
+      <c r="G42" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="I42" s="12">
+        <v>616</v>
+      </c>
+      <c r="J42" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K42" s="15">
+        <v>45</v>
+      </c>
+      <c r="L42" s="15">
+        <v>27720</v>
+      </c>
+      <c r="R42" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Plana 5/8 NR</v>
+      </c>
+      <c r="S42" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="T42" s="22">
+        <v>32</v>
+      </c>
+      <c r="U42" s="21">
+        <v>156</v>
+      </c>
+      <c r="V42" s="21">
+        <v>0</v>
+      </c>
+      <c r="W42" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="X42" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="7:24" hidden="1">
+      <c r="G43" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="H43" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="I43" s="12">
+        <v>120</v>
+      </c>
+      <c r="J43" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K43" s="15">
+        <v>45</v>
+      </c>
+      <c r="L43" s="15">
+        <v>5400</v>
+      </c>
+      <c r="R43" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Perno Hexagonal Grado 2 1/2X1 Pulg ​</v>
+      </c>
+      <c r="S43" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="T43" s="22">
+        <v>103</v>
+      </c>
+      <c r="U43" s="21">
+        <v>268</v>
+      </c>
+      <c r="V43" s="21">
+        <v>0</v>
+      </c>
+      <c r="W43" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="X43" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="7:24" hidden="1">
+      <c r="G44" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="H44" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="I44" s="12">
+        <v>20</v>
+      </c>
+      <c r="J44" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K44" s="15">
+        <v>45</v>
+      </c>
+      <c r="L44" s="15">
+        <v>900</v>
+      </c>
+      <c r="R44" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Perno Hexagonal Grado 2 1/2 x 1.1/2 NR ​</v>
+      </c>
+      <c r="S44" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="T44" s="22">
+        <v>132</v>
+      </c>
+      <c r="U44" s="21">
+        <v>4</v>
+      </c>
+      <c r="V44" s="21">
+        <v>0</v>
+      </c>
+      <c r="W44" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="X44" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="7:24" hidden="1">
+      <c r="G45" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="H45" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="I45" s="12">
+        <v>4</v>
+      </c>
+      <c r="J45" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K45" s="15">
+        <v>45</v>
+      </c>
+      <c r="L45" s="15">
+        <v>180</v>
+      </c>
+      <c r="R45" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Plana 1/2 NR</v>
+      </c>
+      <c r="S45" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="T45" s="22">
+        <v>25</v>
+      </c>
+      <c r="U45" s="21">
+        <v>4</v>
+      </c>
+      <c r="V45" s="21">
+        <v>0</v>
+      </c>
+      <c r="W45" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="X45" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="7:24" hidden="1">
+      <c r="G46" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="H46" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="I46" s="12">
+        <v>280</v>
+      </c>
+      <c r="J46" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K46" s="15">
+        <v>45</v>
+      </c>
+      <c r="L46" s="15">
+        <v>12600</v>
+      </c>
+      <c r="R46" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Presión 1/2 NR</v>
+      </c>
+      <c r="S46" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="T46" s="22">
+        <v>26</v>
+      </c>
+      <c r="U46" s="21">
+        <v>4</v>
+      </c>
+      <c r="V46" s="21">
+        <v>0</v>
+      </c>
+      <c r="W46" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="X46" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="7:24" hidden="1">
+      <c r="G47" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H47" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I47" s="12">
+        <v>1520</v>
+      </c>
+      <c r="J47" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K47" s="15">
+        <v>42</v>
+      </c>
+      <c r="L47" s="15">
+        <v>63840</v>
+      </c>
+      <c r="R47" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Tuerca Hexagonal Grado 2 1/2 NR</v>
+      </c>
+      <c r="S47" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="T47" s="22">
+        <v>45</v>
+      </c>
+      <c r="U47" s="21">
+        <v>4</v>
+      </c>
+      <c r="V47" s="21">
+        <v>0</v>
+      </c>
+      <c r="W47" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="X47" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="7:24" hidden="1">
+      <c r="G48" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="H48" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="I48" s="12">
+        <v>40</v>
+      </c>
+      <c r="J48" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K48" s="15">
+        <v>38</v>
+      </c>
+      <c r="L48" s="15">
+        <v>1520</v>
+      </c>
+      <c r="R48" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Perno Hexagonal Grado 2 1/2 x 1.1/2 NR ​</v>
+      </c>
+      <c r="S48" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="T48" s="22">
+        <v>132</v>
+      </c>
+      <c r="U48" s="21">
+        <v>280</v>
+      </c>
+      <c r="V48" s="21">
+        <v>0</v>
+      </c>
+      <c r="W48" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="X48" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="7:24" hidden="1">
+      <c r="G49" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="H49" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="I49" s="12">
+        <v>80</v>
+      </c>
+      <c r="J49" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K49" s="15">
+        <v>251</v>
+      </c>
+      <c r="L49" s="15">
+        <v>20080</v>
+      </c>
+      <c r="R49" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Plana 1/2 NR</v>
+      </c>
+      <c r="S49" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="T49" s="22">
+        <v>25</v>
+      </c>
+      <c r="U49" s="21">
+        <v>280</v>
+      </c>
+      <c r="V49" s="21">
+        <v>0</v>
+      </c>
+      <c r="W49" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="X49" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="7:24" hidden="1">
+      <c r="G50" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="H50" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="I50" s="12">
+        <v>180</v>
+      </c>
+      <c r="J50" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K50" s="15">
+        <v>22</v>
+      </c>
+      <c r="L50" s="15">
+        <v>3960</v>
+      </c>
+      <c r="R50" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Golilla Presión 1/2 NR</v>
+      </c>
+      <c r="S50" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="T50" s="22">
+        <v>26</v>
+      </c>
+      <c r="U50" s="21">
+        <v>280</v>
+      </c>
+      <c r="V50" s="21">
+        <v>0</v>
+      </c>
+      <c r="W50" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="X50" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="7:24" hidden="1">
+      <c r="G51" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="H51" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="I51" s="12">
+        <v>348</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K51" s="15">
+        <v>22</v>
+      </c>
+      <c r="L51" s="15">
+        <v>7656</v>
+      </c>
+      <c r="R51" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Tuerca Hexagonal Grado 2 1/2 NR</v>
+      </c>
+      <c r="S51" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="T51" s="22">
+        <v>45</v>
+      </c>
+      <c r="U51" s="21">
+        <v>280</v>
+      </c>
+      <c r="V51" s="21">
+        <v>0</v>
+      </c>
+      <c r="W51" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="X51" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="7:24" hidden="1">
+      <c r="G52" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="H52" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="I52" s="12">
+        <v>56</v>
+      </c>
+      <c r="J52" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K52" s="15">
+        <v>88</v>
+      </c>
+      <c r="L52" s="15">
+        <v>4928</v>
+      </c>
+      <c r="R52" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>Perno Hexagonal Grado 2 1/2 x 1.1/2 NR ​</v>
+      </c>
+      <c r="S52" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="T52" s="22">
+        <v>132</v>
+      </c>
+      <c r="U52" s="21">
+        <v>616</v>
+      </c>
+      <c r="V52" s="21">
+        <v>0</v>
+      </c>
+      <c r="W52" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="X52" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="7:24">
+      <c r="G53" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="H53" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="I53" s="12">
+        <v>156</v>
+      </c>
+      <c r="J53" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K53" s="15">
+        <v>88</v>
+      </c>
+      <c r="L53" s="15">
+        <v>13728</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="R1:S52" xr:uid="{07ED76D3-9DCD-AF46-93A0-3260D7DD697E}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Tuerca Hexagonal Grado 2 3/8 NR"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>